--- a/quizzes/033_famous_people_quiz--quizzes.xlsx
+++ b/quizzes/033_famous_people_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'george_washington'}</t>
+          <t>george_washington</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'George Washington'}</t>
+          <t>George Washington</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'abraham_lincoln'}</t>
+          <t>abraham_lincoln</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Abraham Lincoln'}</t>
+          <t>Abraham Lincoln</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'thomas_jefferson'}</t>
+          <t>thomas_jefferson</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Thomas Jefferson'}</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'harper_lee'}</t>
+          <t>harper_lee</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Harper Lee'}</t>
+          <t>Harper Lee</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'f._scott_fitzgerald'}</t>
+          <t>f._scott_fitzgerald</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'F. Scott Fitzgerald'}</t>
+          <t>F. Scott Fitzgerald</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'jane_austen'}</t>
+          <t>jane_austen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Jane Austen'}</t>
+          <t>Jane Austen</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'jodie_foster'}</t>
+          <t>jodie_foster</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Jodie Foster'}</t>
+          <t>Jodie Foster</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'meryl_streep'}</t>
+          <t>meryl_streep</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Meryl Streep'}</t>
+          <t>Meryl Streep</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'judi_dench'}</t>
+          <t>judi_dench</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Judi Dench'}</t>
+          <t>Judi Dench</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'elton_john'}</t>
+          <t>elton_john</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Elton John'}</t>
+          <t>Elton John</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'billy_joel'}</t>
+          <t>billy_joel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Billy Joel'}</t>
+          <t>Billy Joel</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'elton_john'}</t>
+          <t>marlon_brando</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Elton John'}</t>
+          <t>Marlon Brando</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'marlon_brando'}</t>
+          <t>robert_de_niro</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Marlon Brando'}</t>
+          <t>Robert De Niro</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'robert_de_niro'}</t>
+          <t>robert_downey_jr</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Robert De Niro'}</t>
+          <t>Robert Downey Jr</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'robert_downey_jr'}</t>
+          <t>tim_robbins</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Robert Downey Jr'}</t>
+          <t>Tim Robbins</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'tim_robbins'}</t>
+          <t>tom_hanks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Tim Robbins'}</t>
+          <t>Tom Hanks</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tom_hanks'}</t>
+          <t>morgan_freeman</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tom Hanks'}</t>
+          <t>Morgan Freeman</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'morgan_freeman'}</t>
+          <t>leonardo_dicaprio</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Morgan Freeman'}</t>
+          <t>Leonardo DiCaprio</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'leonardo_dicaprio'}</t>
+          <t>kate_winslet</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Leonardo DiCaprio'}</t>
+          <t>Kate Winslet</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'kate_winslet'}</t>
+          <t>billy_zane</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Kate Winslet'}</t>
+          <t>Billy Zane</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'billy_zane'}</t>
+          <t>f._scott_fitzgerald</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Billy Zane'}</t>
+          <t>F. Scott Fitzgerald</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'f._scott_fitzgerald'}</t>
+          <t>ernest_hemingway</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'F. Scott Fitzgerald'}</t>
+          <t>Ernest Hemingway</t>
         </is>
       </c>
     </row>
@@ -1505,29 +1505,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'ernest_hemingway'}</t>
+          <t>john_grisham</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Ernest Hemingway'}</t>
+          <t>John Grisham</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'john_grisham'}</t>
+          <t>elvis_presley</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'John Grisham'}</t>
+          <t>Elvis Presley</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'elvis_presley'}</t>
+          <t>chuck_berry</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Elvis Presley'}</t>
+          <t>Chuck Berry</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'chuck_berry'}</t>
+          <t>little_richard</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Chuck Berry'}</t>
+          <t>Little Richard</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'little_richard'}</t>
+          <t>vincent_van_gogh</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Little Richard'}</t>
+          <t>Vincent van Gogh</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'vincent_van_gogh'}</t>
+          <t>pablo_picasso</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Vincent van Gogh'}</t>
+          <t>Pablo Picasso</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pablo_picasso'}</t>
+          <t>claude_monet</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Pablo Picasso'}</t>
+          <t>Claude Monet</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'claude_monet'}</t>
+          <t>vincent_van_gogh</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Claude Monet'}</t>
+          <t>Vincent van Gogh</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'vincent_van_gogh'}</t>
+          <t>salvador_dali</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Vincent van Gogh'}</t>
+          <t>Salvador Dali</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'salvador_dali'}</t>
+          <t>edvard_munch</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Salvador Dali'}</t>
+          <t>Edvard Munch</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'edvard_munch'}</t>
+          <t>madonna</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Edvard Munch'}</t>
+          <t>Madonna</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'madonna'}</t>
+          <t>lady_gaga</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Madonna'}</t>
+          <t>Lady Gaga</t>
         </is>
       </c>
     </row>
@@ -1709,29 +1709,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'lady_gaga'}</t>
+          <t>elton_john</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Lady Gaga'}</t>
+          <t>Elton John</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'elton_john'}</t>
+          <t>heath_ledger</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Elton John'}</t>
+          <t>Heath Ledger</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'heath_ledger'}</t>
+          <t>christian_bale</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Heath Ledger'}</t>
+          <t>Christian Bale</t>
         </is>
       </c>
     </row>
@@ -1760,29 +1760,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'christian_bale'}</t>
+          <t>robert_downey_jr</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Christian Bale'}</t>
+          <t>Robert Downey Jr</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'robert_downey_jr'}</t>
+          <t>j.r.r._tolkien</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Robert Downey Jr'}</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'j.r.r._tolkien'}</t>
+          <t>j.k._rowling</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'J.R.R. Tolkien'}</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
     </row>
@@ -1811,29 +1811,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'j.k._rowling'}</t>
+          <t>george_r._r._martin</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'J.K. Rowling'}</t>
+          <t>George R. R. Martin</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'george_r._r._martin'}</t>
+          <t>eric_clapton</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'George R. R. Martin'}</t>
+          <t>Eric Clapton</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'eric_clapton'}</t>
+          <t>jimmy_page</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Eric Clapton'}</t>
+          <t>Jimmy Page</t>
         </is>
       </c>
     </row>
@@ -1862,29 +1862,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'jimmy_page'}</t>
+          <t>prince</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Jimmy Page'}</t>
+          <t>Prince</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'prince'}</t>
+          <t>jodie_foster</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Prince'}</t>
+          <t>Jodie Foster</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'jodie_foster'}</t>
+          <t>meryl_streep</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Jodie Foster'}</t>
+          <t>Meryl Streep</t>
         </is>
       </c>
     </row>
@@ -1913,29 +1913,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'meryl_streep'}</t>
+          <t>judi_dench</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Meryl Streep'}</t>
+          <t>Judi Dench</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'judi_dench'}</t>
+          <t>harper_lee</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Judi Dench'}</t>
+          <t>Harper Lee</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'harper_lee'}</t>
+          <t>f._scott_fitzgerald</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Harper Lee'}</t>
+          <t>F. Scott Fitzgerald</t>
         </is>
       </c>
     </row>
@@ -1964,29 +1964,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'f._scott_fitzgerald'}</t>
+          <t>jane_austen</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'F. Scott Fitzgerald'}</t>
+          <t>Jane Austen</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>question_17_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'jane_austen'}</t>
+          <t>aretha_franklin</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Jane Austen'}</t>
+          <t>Aretha Franklin</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'aretha_franklin'}</t>
+          <t>tina_turner</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Aretha Franklin'}</t>
+          <t>Tina Turner</t>
         </is>
       </c>
     </row>
@@ -2015,29 +2015,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tina_turner'}</t>
+          <t>patsy_cline</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tina Turner'}</t>
+          <t>Patsy Cline</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>question_19_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'patsy_cline'}</t>
+          <t>marlon_brando</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Patsy Cline'}</t>
+          <t>Marlon Brando</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'marlon_brando'}</t>
+          <t>robert_de_niro</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Marlon Brando'}</t>
+          <t>Robert De Niro</t>
         </is>
       </c>
     </row>
@@ -2066,29 +2066,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'robert_de_niro'}</t>
+          <t>robert_downey</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Robert De Niro'}</t>
+          <t>Robert Downey</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>question_19_choices</t>
+          <t>question_20_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'robert_downey'}</t>
+          <t>f._scott_fitzgerald</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Robert Downey'}</t>
+          <t>F. Scott Fitzgerald</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'f._scott_fitzgerald'}</t>
+          <t>ernest_hemingway</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'F. Scott Fitzgerald'}</t>
+          <t>Ernest Hemingway</t>
         </is>
       </c>
     </row>
@@ -2117,29 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'ernest_hemingway'}</t>
+          <t>john_grisham</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Ernest Hemingway'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'john_grisham'}</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'John Grisham'}</t>
+          <t>John Grisham</t>
         </is>
       </c>
     </row>
